--- a/data/trans_dic/IP1005-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen anomalía congénita</t>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,98</t>
+          <t>0,32; 2,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,62</t>
+          <t>0,2; 2,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,16; 1,82</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,84</t>
+          <t>0,09; 0,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,73</t>
+          <t>0,06; 0,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,14</t>
+          <t>0,2; 1,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,61</t>
+          <t>0,13; 0,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,49</t>
+          <t>0,08; 0,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,75</t>
+          <t>0,23; 0,76</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2345</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2255</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3032</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2795</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3360</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3156</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4490</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2236</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3582</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3266</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2259</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4368</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3928</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3793</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4215</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4266</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3108</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3395</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3517</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4084</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3372</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3581</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2864</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2408</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4825</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4081</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>546; 4941</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>635; 6577</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4650</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>550; 6082</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>633; 5188</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>442; 5273</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>604; 5967</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>601; 5345</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4076</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1469; 8101</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1816; 8600</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1125; 6799</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3278; 11035</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1005-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Provincia-trans_dic.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,89</t>
+          <t>0,32; 2,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,04</t>
+          <t>0,19; 1,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,82</t>
+          <t>0,2; 1,6</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,76</t>
+          <t>0,09; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,75</t>
+          <t>0,06; 0,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,07; 0,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,08; 0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,09</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,61</t>
+          <t>0,1; 0,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,47</t>
+          <t>0,08; 0,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,76</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2345</t>
+          <t>0; 2696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2255</t>
+          <t>0; 2703</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>0; 3165</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2795</t>
+          <t>0; 3010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3360</t>
+          <t>0; 4050</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3156</t>
+          <t>0; 3554</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4490</t>
+          <t>0; 4176</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2236</t>
+          <t>0; 2108</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3582</t>
+          <t>0; 3736</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>0; 3855</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2259</t>
+          <t>0; 2670</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4368</t>
+          <t>0; 4795</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3928</t>
+          <t>0; 3975</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3793</t>
+          <t>0; 3813</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4215</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4266</t>
+          <t>0; 3432</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>0; 3459</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3395</t>
+          <t>0; 3780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3517</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4084</t>
+          <t>0; 5358</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3372</t>
+          <t>0; 3371</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3581</t>
+          <t>0; 3536</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2864</t>
+          <t>0; 3303</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2408</t>
+          <t>0; 2729</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4825</t>
+          <t>0; 5067</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4081</t>
+          <t>0; 3375</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>546; 4941</t>
+          <t>544; 4976</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>635; 6577</t>
+          <t>607; 5291</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4650</t>
+          <t>0; 4686</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>550; 6082</t>
+          <t>676; 5360</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>633; 5188</t>
+          <t>633; 4664</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>442; 5273</t>
+          <t>437; 4903</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>604; 5967</t>
+          <t>484; 5665</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>601; 5345</t>
+          <t>602; 6019</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 4076</t>
+          <t>0; 4745</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1469; 8101</t>
+          <t>1383; 8190</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1816; 8600</t>
+          <t>1346; 8294</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1125; 6799</t>
+          <t>1103; 7333</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3278; 11035</t>
+          <t>3201; 11555</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1005-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,22 +635,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,83%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
     </row>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,32; 2,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,64</t>
+          <t>0,19; 1,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,6</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,68</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,69</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,18; 1,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,83</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,06; 0,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,1</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,59</t>
+          <t>0,1; 0,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,5</t>
+          <t>0,08; 0,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,21; 0,75</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1765,22 +1765,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1818,22 +1818,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>477</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2736</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2703</t>
+          <t>0; 2400</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>604</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3165</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3010</t>
+          <t>0; 3655</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3585</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 3055</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3554</t>
+          <t>0; 3176</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4176</t>
+          <t>0; 4608</t>
         </is>
       </c>
     </row>
@@ -2249,22 +2249,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2302,27 +2302,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>759</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2108</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3736</t>
+          <t>0; 3058</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2700</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3855</t>
+          <t>0; 4264</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2670</t>
+          <t>0; 2435</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4795</t>
+          <t>0; 4663</t>
         </is>
       </c>
     </row>
@@ -2575,14 +2575,14 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2628,27 +2628,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3522</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3813</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>0; 3992</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3432</t>
+          <t>0; 4071</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3459</t>
+          <t>0; 3660</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3780</t>
+          <t>0; 3371</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3311</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 5358</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3371</t>
+          <t>0; 3830</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>479</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3536</t>
+          <t>0; 4227</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3303</t>
+          <t>0; 3404</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2729</t>
+          <t>546; 5084</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 5067</t>
+          <t>0; 3598</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3375</t>
+          <t>0; 3802</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>544; 4976</t>
+          <t>0; 2558</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>607; 5291</t>
+          <t>598; 5223</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4686</t>
+          <t>0; 5484</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>676; 5360</t>
+          <t>550; 5336</t>
         </is>
       </c>
     </row>
@@ -3064,27 +3064,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>2319</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>633; 4664</t>
+          <t>602; 5793</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>437; 4903</t>
+          <t>0; 4724</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>484; 5665</t>
+          <t>1359; 8470</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>602; 6019</t>
+          <t>632; 5742</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 4745</t>
+          <t>442; 5184</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1383; 8190</t>
+          <t>605; 5496</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1346; 8294</t>
+          <t>1373; 8619</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1103; 7333</t>
+          <t>1121; 7188</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3201; 11555</t>
+          <t>3054; 10897</t>
         </is>
       </c>
     </row>
